--- a/docs/lem/files/xslope_earth_dam_rapid.xlsx
+++ b/docs/lem/files/xslope_earth_dam_rapid.xlsx
@@ -629,7 +629,7 @@
     <t>* piezometric line 2 is only required for rapid drawdown analysis</t>
   </si>
   <si>
-    <t>Type optons</t>
+    <t>Type options</t>
   </si>
   <si>
     <t>True piezometric line: u = γw × vertical distance below the line (static head).</t>
@@ -638,7 +638,7 @@
     <t>phreatic</t>
   </si>
   <si>
-    <t xml:space="preserve"> Phreatic surface: static head reduced by cos² of the line's slope.</t>
+    <t>Phreatic surface: static head reduced by cos² of the line's slope.</t>
   </si>
   <si>
     <t>#</t>
@@ -8584,7 +8584,9 @@
       <c r="C11" s="3">
         <v>125.0</v>
       </c>
-      <c r="D11" s="3"/>
+      <c r="D11" s="3">
+        <v>130.0</v>
+      </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
           <t>mc</t>
@@ -8709,7 +8711,9 @@
       <c r="C12" s="3">
         <v>122.0</v>
       </c>
-      <c r="D12" s="3"/>
+      <c r="D12" s="3">
+        <v>127.0</v>
+      </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
           <t>mc</t>
@@ -8838,7 +8842,9 @@
       <c r="C13" s="3">
         <v>123.0</v>
       </c>
-      <c r="D13" s="3"/>
+      <c r="D13" s="3">
+        <v>128.0</v>
+      </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
           <t>mc</t>
@@ -8967,7 +8973,9 @@
       <c r="C14" s="3">
         <v>127.0</v>
       </c>
-      <c r="D14" s="3"/>
+      <c r="D14" s="3">
+        <v>132.0</v>
+      </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
           <t>mc</t>

--- a/docs/lem/files/xslope_earth_dam_rapid.xlsx
+++ b/docs/lem/files/xslope_earth_dam_rapid.xlsx
@@ -3277,7 +3277,7 @@
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
-          <t>day</t>
+          <t>min</t>
         </is>
       </c>
       <c r="F9" s="1" t="s">
@@ -6558,13 +6558,13 @@
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
-        <v>320.0</v>
+        <v>311.0</v>
       </c>
       <c r="C5" s="3">
         <v>317.0</v>
       </c>
       <c r="E5" s="3">
-        <v>-150.0</v>
+        <v>-158.0</v>
       </c>
       <c r="F5" s="3">
         <v>227.0</v>
@@ -6586,7 +6586,7 @@
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
-        <v>590.0</v>
+        <v>581.0</v>
       </c>
       <c r="C6" s="3">
         <v>227.0</v>
@@ -6612,7 +6612,7 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
-        <v>740.0</v>
+        <v>638.0</v>
       </c>
       <c r="C7" s="3">
         <v>227.0</v>
@@ -7004,13 +7004,13 @@
     </row>
     <row r="5" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B5" s="3">
-        <v>320.0</v>
+        <v>311.0</v>
       </c>
       <c r="C5" s="3">
         <v>317.0</v>
       </c>
       <c r="E5" s="3">
-        <v>-150.0</v>
+        <v>-158.0</v>
       </c>
       <c r="F5" s="3">
         <v>227.0</v>
@@ -7032,7 +7032,7 @@
     </row>
     <row r="6" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B6" s="3">
-        <v>590.0</v>
+        <v>581.0</v>
       </c>
       <c r="C6" s="3">
         <v>227.0</v>
@@ -7054,7 +7054,7 @@
     </row>
     <row r="7" spans="2:21" x14ac:dyDescent="0.2">
       <c r="B7" s="3">
-        <v>740.0</v>
+        <v>638.0</v>
       </c>
       <c r="C7" s="3">
         <v>227.0</v>
@@ -8668,10 +8668,10 @@
         <v>0.0</v>
       </c>
       <c r="AG11" s="3">
-        <v>864.0</v>
+        <v>0.01</v>
       </c>
       <c r="AH11" s="3">
-        <v>864.0</v>
+        <v>0.01</v>
       </c>
       <c r="AI11" s="3">
         <v>0.0</v>
@@ -8799,10 +8799,10 @@
         <v>0.0</v>
       </c>
       <c r="AG12" s="3">
-        <v>0.0864</v>
+        <v>1e-06</v>
       </c>
       <c r="AH12" s="3">
-        <v>0.0864</v>
+        <v>1e-06</v>
       </c>
       <c r="AI12" s="3">
         <v>0.0</v>
@@ -8930,10 +8930,10 @@
         <v>0.0</v>
       </c>
       <c r="AG13" s="3">
-        <v>0.864</v>
+        <v>1e-05</v>
       </c>
       <c r="AH13" s="3">
-        <v>0.864</v>
+        <v>1e-05</v>
       </c>
       <c r="AI13" s="3">
         <v>0.0</v>
@@ -9057,10 +9057,10 @@
         <v>0.0</v>
       </c>
       <c r="AG14" s="3">
-        <v>86.4</v>
+        <v>0.001</v>
       </c>
       <c r="AH14" s="3">
-        <v>86.4</v>
+        <v>0.001</v>
       </c>
       <c r="AI14" s="3">
         <v>0.0</v>
@@ -10847,19 +10847,19 @@
         <v>227.0</v>
       </c>
       <c r="D9" s="3">
-        <v>240.0</v>
+        <v>237.0</v>
       </c>
       <c r="E9" s="3">
         <v>227.0</v>
       </c>
       <c r="G9" s="3">
-        <v>-150.0</v>
+        <v>-158.0</v>
       </c>
       <c r="H9" s="3">
         <v>227.0</v>
       </c>
       <c r="J9" s="3">
-        <v>-150.0</v>
+        <v>-158.0</v>
       </c>
       <c r="K9" s="3">
         <v>197.0</v>
@@ -10903,19 +10903,19 @@
         <v>317.0</v>
       </c>
       <c r="D10" s="3">
-        <v>280.0</v>
+        <v>278.0</v>
       </c>
       <c r="E10" s="3">
-        <v>307.0</v>
+        <v>309.0</v>
       </c>
       <c r="G10" s="3">
-        <v>740.0</v>
+        <v>638.0</v>
       </c>
       <c r="H10" s="3">
         <v>227.0</v>
       </c>
       <c r="J10" s="3">
-        <v>740.0</v>
+        <v>638.0</v>
       </c>
       <c r="K10" s="3">
         <v>197.0</v>
@@ -10953,16 +10953,16 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A11" s="3">
-        <v>320.0</v>
+        <v>311.0</v>
       </c>
       <c r="B11" s="3">
         <v>317.0</v>
       </c>
       <c r="D11" s="3">
-        <v>310.0</v>
+        <v>304.0</v>
       </c>
       <c r="E11" s="3">
-        <v>307.0</v>
+        <v>309.0</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
@@ -11001,13 +11001,13 @@
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A12" s="3">
-        <v>590.0</v>
+        <v>581.0</v>
       </c>
       <c r="B12" s="3">
         <v>227.0</v>
       </c>
       <c r="D12" s="3">
-        <v>350.0</v>
+        <v>345.0</v>
       </c>
       <c r="E12" s="3">
         <v>227.0</v>
